--- a/jogos_2025-09-09.xlsx
+++ b/jogos_2025-09-09.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X2" t="n">
         <v>2.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC2" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>

--- a/jogos_2025-09-09.xlsx
+++ b/jogos_2025-09-09.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L2" t="n">

--- a/jogos_2025-09-09.xlsx
+++ b/jogos_2025-09-09.xlsx
@@ -708,7 +708,7 @@
         <v>2.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Z2" t="n">
         <v>1.88</v>

--- a/jogos_2025-09-09.xlsx
+++ b/jogos_2025-09-09.xlsx
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
         <v>2.62</v>
@@ -699,25 +699,25 @@
         <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="X2" t="n">
-        <v>2.92</v>
+        <v>3.72</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Z2" t="n">
         <v>1.88</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AC2" t="n">
         <v>1.7</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
         <v>1.44</v>

--- a/jogos_2025-09-09.xlsx
+++ b/jogos_2025-09-09.xlsx
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="N2" t="n">
         <v>2.62</v>
@@ -702,22 +702,22 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X2" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
         <v>1.7</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
         <v>1.44</v>

--- a/jogos_2025-09-09.xlsx
+++ b/jogos_2025-09-09.xlsx
@@ -652,100 +652,100 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="M2" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.62</v>
       </c>
-      <c r="O2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.8</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
         <v>1.25</v>
       </c>
       <c r="X2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '34']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45909.47916666666</v>
